--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -456,26 +466,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad Pos 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.33873</v>
+        <v>17.34275</v>
       </c>
       <c r="D2" t="n">
-        <v>17.59685</v>
+        <v>17.02125</v>
       </c>
       <c r="E2" t="n">
-        <v>17.52156</v>
+        <v>17.30679</v>
       </c>
       <c r="F2" t="n">
-        <v>42.58202</v>
+        <v>57.55386</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05187</v>
+        <v>44.1647</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88332</v>
+        <v>87.34519</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05291</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.89707</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.63065</v>
+        <v>17.07744</v>
       </c>
       <c r="D3" t="n">
-        <v>17.52191</v>
+        <v>16.89333</v>
       </c>
       <c r="E3" t="n">
-        <v>17.50149</v>
+        <v>17.03013</v>
       </c>
       <c r="F3" t="n">
-        <v>43.73545</v>
+        <v>57.02733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05132</v>
+        <v>43.54967</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91232</v>
+        <v>86.60997999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05288</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.87974</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.45877</v>
+        <v>17.53692</v>
       </c>
       <c r="D4" t="n">
-        <v>16.84545</v>
+        <v>17.21134</v>
       </c>
       <c r="E4" t="n">
-        <v>17.54224</v>
+        <v>17.38111</v>
       </c>
       <c r="F4" t="n">
-        <v>44.28315</v>
+        <v>57.65871</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0524</v>
+        <v>42.74007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86604</v>
+        <v>87.45143</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05233</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.87152</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.1581</v>
+        <v>17.54478</v>
       </c>
       <c r="D5" t="n">
-        <v>16.93401</v>
+        <v>17.02879</v>
       </c>
       <c r="E5" t="n">
-        <v>17.10409</v>
+        <v>17.34681</v>
       </c>
       <c r="F5" t="n">
-        <v>44.29042</v>
+        <v>56.78839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05289</v>
+        <v>44.52117</v>
       </c>
       <c r="H5" t="n">
-        <v>1.89516</v>
+        <v>86.40746</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05161</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.86363</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.36501</v>
+        <v>17.63134</v>
       </c>
       <c r="D6" t="n">
-        <v>17.36508</v>
+        <v>16.87478</v>
       </c>
       <c r="E6" t="n">
-        <v>17.09021</v>
+        <v>17.02279</v>
       </c>
       <c r="F6" t="n">
-        <v>43.09904</v>
+        <v>57.58467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05359</v>
+        <v>42.91649</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88133</v>
+        <v>88.23618999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.89564</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.04863</v>
+        <v>17.51462</v>
       </c>
       <c r="D7" t="n">
-        <v>17.08733</v>
+        <v>17.04937</v>
       </c>
       <c r="E7" t="n">
-        <v>17.06577</v>
+        <v>17.27721</v>
       </c>
       <c r="F7" t="n">
-        <v>43.30519</v>
+        <v>58.37394</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05221</v>
+        <v>43.90138</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88923</v>
+        <v>88.27907999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.87004</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.23435</v>
+        <v>17.48159</v>
       </c>
       <c r="D8" t="n">
-        <v>17.27752</v>
+        <v>17.2626</v>
       </c>
       <c r="E8" t="n">
-        <v>17.58272</v>
+        <v>17.3667</v>
       </c>
       <c r="F8" t="n">
-        <v>43.94609</v>
+        <v>55.67475</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05215</v>
+        <v>43.19517</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85729</v>
+        <v>86.3772</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05324</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.90499</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.33878</v>
+        <v>17.23796</v>
       </c>
       <c r="D9" t="n">
-        <v>16.82969</v>
+        <v>16.93864</v>
       </c>
       <c r="E9" t="n">
-        <v>16.84563</v>
+        <v>17.03748</v>
       </c>
       <c r="F9" t="n">
-        <v>43.60469</v>
+        <v>57.888</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05211</v>
+        <v>44.61918</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84711</v>
+        <v>86.46683</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.83164</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.1364</v>
+        <v>17.44461</v>
       </c>
       <c r="D10" t="n">
-        <v>17.41733</v>
+        <v>17.35876</v>
       </c>
       <c r="E10" t="n">
-        <v>17.5176</v>
+        <v>17.36432</v>
       </c>
       <c r="F10" t="n">
-        <v>43.17269</v>
+        <v>57.01458</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0516</v>
+        <v>43.84878</v>
       </c>
       <c r="H10" t="n">
-        <v>1.90701</v>
+        <v>86.94307999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05208</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.8873</v>
       </c>
     </row>
     <row r="11">
@@ -696,15 +760,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -718,26 +792,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad Pos 2</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.87523</v>
+        <v>17.35997</v>
       </c>
       <c r="D12" t="n">
-        <v>16.85857</v>
+        <v>17.1164</v>
       </c>
       <c r="E12" t="n">
-        <v>16.97767</v>
+        <v>17.27019</v>
       </c>
       <c r="F12" t="n">
-        <v>44.30316</v>
+        <v>57.21694</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05281</v>
+        <v>43.45826</v>
       </c>
       <c r="H12" t="n">
-        <v>1.86756</v>
+        <v>86.06202999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05125</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.88808</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.22265</v>
+        <v>17.07831</v>
       </c>
       <c r="D13" t="n">
-        <v>17.28591</v>
+        <v>16.82576</v>
       </c>
       <c r="E13" t="n">
-        <v>17.28618</v>
+        <v>16.99937</v>
       </c>
       <c r="F13" t="n">
-        <v>42.77421</v>
+        <v>58.2564</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05249</v>
+        <v>42.8652</v>
       </c>
       <c r="H13" t="n">
-        <v>1.90661</v>
+        <v>87.26441</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.91955</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.3165</v>
+        <v>17.15635</v>
       </c>
       <c r="D14" t="n">
-        <v>17.49869</v>
+        <v>16.76085</v>
       </c>
       <c r="E14" t="n">
-        <v>17.2402</v>
+        <v>17.04465</v>
       </c>
       <c r="F14" t="n">
-        <v>43.7132</v>
+        <v>57.232</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05197</v>
+        <v>42.77546</v>
       </c>
       <c r="H14" t="n">
-        <v>1.87329</v>
+        <v>88.35565</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05214</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.89311</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.11133</v>
+        <v>17.28591</v>
       </c>
       <c r="D15" t="n">
-        <v>17.2384</v>
+        <v>17.03085</v>
       </c>
       <c r="E15" t="n">
-        <v>16.97165</v>
+        <v>17.11032</v>
       </c>
       <c r="F15" t="n">
-        <v>43.31705</v>
+        <v>57.59305</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05386</v>
+        <v>43.61085</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81567</v>
+        <v>87.66649</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.91619</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.06617</v>
+        <v>17.56543</v>
       </c>
       <c r="D16" t="n">
-        <v>16.90558</v>
+        <v>17.15207</v>
       </c>
       <c r="E16" t="n">
-        <v>17.24064</v>
+        <v>17.56444</v>
       </c>
       <c r="F16" t="n">
-        <v>43.45256</v>
+        <v>58.15195</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05201</v>
+        <v>44.35084</v>
       </c>
       <c r="H16" t="n">
-        <v>1.88578</v>
+        <v>87.64578</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05236</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.86839</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.12294</v>
+        <v>17.43134</v>
       </c>
       <c r="D17" t="n">
-        <v>16.61654</v>
+        <v>16.81671</v>
       </c>
       <c r="E17" t="n">
-        <v>17.4968</v>
+        <v>17.3257</v>
       </c>
       <c r="F17" t="n">
-        <v>43.58881</v>
+        <v>57.98722</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05167</v>
+        <v>43.49948</v>
       </c>
       <c r="H17" t="n">
-        <v>1.84366</v>
+        <v>87.32254</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.89134</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.35814</v>
+        <v>17.56623</v>
       </c>
       <c r="D18" t="n">
-        <v>17.0902</v>
+        <v>17.05626</v>
       </c>
       <c r="E18" t="n">
-        <v>17.36744</v>
+        <v>17.48748</v>
       </c>
       <c r="F18" t="n">
-        <v>43.16869</v>
+        <v>57.07188</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05257</v>
+        <v>43.46636</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87034</v>
+        <v>86.64621</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05249</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.87484</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.81322</v>
+        <v>17.34381</v>
       </c>
       <c r="D19" t="n">
-        <v>16.99131</v>
+        <v>17.14459</v>
       </c>
       <c r="E19" t="n">
-        <v>17.30342</v>
+        <v>17.27333</v>
       </c>
       <c r="F19" t="n">
-        <v>43.83085</v>
+        <v>58.63253</v>
       </c>
       <c r="G19" t="n">
-        <v>0.052</v>
+        <v>43.66697</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84132</v>
+        <v>88.78945</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.87861</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +1044,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.352</v>
+        <v>17.45394</v>
       </c>
       <c r="D20" t="n">
-        <v>17.08042</v>
+        <v>16.95288</v>
       </c>
       <c r="E20" t="n">
-        <v>17.17947</v>
+        <v>17.2024</v>
       </c>
       <c r="F20" t="n">
-        <v>42.6434</v>
+        <v>58.26039</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05168</v>
+        <v>43.59689</v>
       </c>
       <c r="H20" t="n">
-        <v>1.87347</v>
+        <v>87.55857</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05347</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.88082</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +1086,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -970,20 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad Pos 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.0318</v>
+        <v>17.2986</v>
       </c>
       <c r="D22" t="n">
-        <v>15.8315</v>
+        <v>16.24305</v>
       </c>
       <c r="E22" t="n">
-        <v>16.11534</v>
+        <v>16.95417</v>
       </c>
       <c r="F22" t="n">
-        <v>267.27633</v>
+        <v>22.40192</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.27063</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.28519</v>
+        <v>17.11804</v>
       </c>
       <c r="D23" t="n">
-        <v>16.02829</v>
+        <v>15.92175</v>
       </c>
       <c r="E23" t="n">
-        <v>16.11772</v>
+        <v>16.77983</v>
       </c>
       <c r="F23" t="n">
-        <v>256.93468</v>
+        <v>22.55585</v>
+      </c>
+      <c r="G23" t="n">
+        <v>35.00647</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.60251</v>
+        <v>17.20631</v>
       </c>
       <c r="D24" t="n">
-        <v>16.20038</v>
+        <v>16.64147</v>
       </c>
       <c r="E24" t="n">
-        <v>16.00207</v>
+        <v>16.85947</v>
       </c>
       <c r="F24" t="n">
-        <v>257.4696</v>
+        <v>21.91824</v>
+      </c>
+      <c r="G24" t="n">
+        <v>35.32458</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.8819</v>
+        <v>17.22634</v>
       </c>
       <c r="D25" t="n">
-        <v>16.41226</v>
+        <v>16.72203</v>
       </c>
       <c r="E25" t="n">
-        <v>16.17769</v>
+        <v>16.76524</v>
       </c>
       <c r="F25" t="n">
-        <v>264.68996</v>
+        <v>22.26754</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35.59967</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.03665</v>
+        <v>17.28381</v>
       </c>
       <c r="D26" t="n">
-        <v>16.1543</v>
+        <v>16.41287</v>
       </c>
       <c r="E26" t="n">
-        <v>15.95</v>
+        <v>17.05611</v>
       </c>
       <c r="F26" t="n">
-        <v>263.55229</v>
+        <v>22.49722</v>
+      </c>
+      <c r="G26" t="n">
+        <v>34.77329</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.27342</v>
+        <v>16.94183</v>
       </c>
       <c r="D27" t="n">
-        <v>15.52941</v>
+        <v>15.98351</v>
       </c>
       <c r="E27" t="n">
-        <v>16.14626</v>
+        <v>16.79809</v>
       </c>
       <c r="F27" t="n">
-        <v>262.23506</v>
+        <v>22.1004</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34.55937</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.76429</v>
+        <v>17.23725</v>
       </c>
       <c r="D28" t="n">
-        <v>15.76062</v>
+        <v>16.56707</v>
       </c>
       <c r="E28" t="n">
-        <v>16.13247</v>
+        <v>17.16393</v>
       </c>
       <c r="F28" t="n">
-        <v>261.26859</v>
+        <v>22.37593</v>
+      </c>
+      <c r="G28" t="n">
+        <v>35.50048</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.12083</v>
+        <v>17.1354</v>
       </c>
       <c r="D29" t="n">
-        <v>16.03814</v>
+        <v>16.51904</v>
       </c>
       <c r="E29" t="n">
-        <v>16.29683</v>
+        <v>16.89551</v>
       </c>
       <c r="F29" t="n">
-        <v>261.93981</v>
+        <v>22.60927</v>
+      </c>
+      <c r="G29" t="n">
+        <v>34.72971</v>
       </c>
     </row>
     <row r="30">
@@ -1126,42 +1283,60 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.36678</v>
+        <v>17.43159</v>
       </c>
       <c r="D30" t="n">
-        <v>16.18091</v>
+        <v>16.3099</v>
       </c>
       <c r="E30" t="n">
-        <v>16.30144</v>
+        <v>16.51551</v>
       </c>
       <c r="F30" t="n">
-        <v>261.60949</v>
+        <v>22.65167</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34.81025</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Rz mean</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Rz min</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
         </is>
       </c>
     </row>
@@ -1173,23 +1348,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace Pos 1</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.37872</v>
+        <v>0.77294</v>
       </c>
       <c r="D32" t="n">
-        <v>16.43064</v>
+        <v>0.08315</v>
       </c>
       <c r="E32" t="n">
-        <v>16.99101</v>
+        <v>0.62886</v>
       </c>
       <c r="F32" t="n">
-        <v>22.3963</v>
+        <v>0.98247</v>
       </c>
       <c r="G32" t="n">
-        <v>34.69018</v>
+        <v>0.1118</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09719</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12842</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1383,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.38981</v>
+        <v>0.76731</v>
       </c>
       <c r="D33" t="n">
-        <v>16.37964</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>16.80656</v>
+        <v>0.62015</v>
       </c>
       <c r="F33" t="n">
-        <v>22.36355</v>
+        <v>0.97962</v>
       </c>
       <c r="G33" t="n">
-        <v>34.76108</v>
+        <v>0.11442</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09591</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12953</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1414,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.60963</v>
+        <v>0.7569</v>
       </c>
       <c r="D34" t="n">
-        <v>16.59115</v>
+        <v>0.08447</v>
       </c>
       <c r="E34" t="n">
-        <v>16.47153</v>
+        <v>0.61792</v>
       </c>
       <c r="F34" t="n">
-        <v>22.22367</v>
+        <v>0.99194</v>
       </c>
       <c r="G34" t="n">
-        <v>35.09641</v>
+        <v>0.11391</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09585</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12925</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1445,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.34297</v>
+        <v>0.79004</v>
       </c>
       <c r="D35" t="n">
-        <v>16.36715</v>
+        <v>0.08295</v>
       </c>
       <c r="E35" t="n">
-        <v>16.67216</v>
+        <v>0.62259</v>
       </c>
       <c r="F35" t="n">
-        <v>21.79952</v>
+        <v>0.97917</v>
       </c>
       <c r="G35" t="n">
-        <v>34.46403</v>
+        <v>0.11026</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09585</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12801</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1476,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17.21256</v>
+        <v>0.75392</v>
       </c>
       <c r="D36" t="n">
-        <v>16.60265</v>
+        <v>0.0834</v>
       </c>
       <c r="E36" t="n">
-        <v>16.62567</v>
+        <v>0.62706</v>
       </c>
       <c r="F36" t="n">
-        <v>22.78799</v>
+        <v>0.9969</v>
       </c>
       <c r="G36" t="n">
-        <v>34.94215</v>
+        <v>0.11472</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.13141</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1507,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17.06546</v>
+        <v>0.7680399999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>16.64143</v>
+        <v>0.08214</v>
       </c>
       <c r="E37" t="n">
-        <v>17.29455</v>
+        <v>0.64339</v>
       </c>
       <c r="F37" t="n">
-        <v>22.74576</v>
+        <v>0.97684</v>
       </c>
       <c r="G37" t="n">
-        <v>35.24292</v>
+        <v>0.11423</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09789</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12954</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1538,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17.00021</v>
+        <v>0.77721</v>
       </c>
       <c r="D38" t="n">
-        <v>16.49153</v>
+        <v>0.08218</v>
       </c>
       <c r="E38" t="n">
-        <v>16.75466</v>
+        <v>0.6218900000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>22.31148</v>
+        <v>0.98412</v>
       </c>
       <c r="G38" t="n">
-        <v>35.34574</v>
+        <v>0.11468</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09687999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12837</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1569,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.92544</v>
+        <v>0.76664</v>
       </c>
       <c r="D39" t="n">
-        <v>16.59727</v>
+        <v>0.08348999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>16.75135</v>
+        <v>0.61424</v>
       </c>
       <c r="F39" t="n">
-        <v>22.17697</v>
+        <v>0.9876200000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>36.14571</v>
+        <v>0.11493</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09447</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12836</v>
       </c>
     </row>
     <row r="40">
@@ -1353,677 +1600,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.21773</v>
+        <v>0.76375</v>
       </c>
       <c r="D40" t="n">
-        <v>16.74661</v>
+        <v>0.08444</v>
       </c>
       <c r="E40" t="n">
-        <v>16.83031</v>
+        <v>0.62681</v>
       </c>
       <c r="F40" t="n">
-        <v>22.75041</v>
+        <v>0.97949</v>
       </c>
       <c r="G40" t="n">
-        <v>35.55785</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Via Pos 1</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.63484</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.13049</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0.62359</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.15062</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0.62614</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.16061</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.62579</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.13861</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.6282</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.16141</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.62527</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1.1386</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.61244</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1.15443</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.62085</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.13786</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.62187</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.1511</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Landing Pad 1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>17.35471</v>
-      </c>
-      <c r="D52" t="n">
-        <v>16.96189</v>
-      </c>
-      <c r="E52" t="n">
-        <v>17.03802</v>
-      </c>
-      <c r="F52" t="n">
-        <v>43.86278</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>16.98598</v>
-      </c>
-      <c r="D53" t="n">
-        <v>17.08516</v>
-      </c>
-      <c r="E53" t="n">
-        <v>17.33641</v>
-      </c>
-      <c r="F53" t="n">
-        <v>43.76338</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>17.40801</v>
-      </c>
-      <c r="D54" t="n">
-        <v>17.23944</v>
-      </c>
-      <c r="E54" t="n">
-        <v>16.77511</v>
-      </c>
-      <c r="F54" t="n">
-        <v>43.97398</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>16.92779</v>
-      </c>
-      <c r="D55" t="n">
-        <v>17.03039</v>
-      </c>
-      <c r="E55" t="n">
-        <v>17.13201</v>
-      </c>
-      <c r="F55" t="n">
-        <v>43.83808</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>17.16862</v>
-      </c>
-      <c r="D56" t="n">
-        <v>16.52069</v>
-      </c>
-      <c r="E56" t="n">
-        <v>17.09077</v>
-      </c>
-      <c r="F56" t="n">
-        <v>42.94701</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>17.26684</v>
-      </c>
-      <c r="D57" t="n">
-        <v>17.03212</v>
-      </c>
-      <c r="E57" t="n">
-        <v>17.10209</v>
-      </c>
-      <c r="F57" t="n">
-        <v>43.49558</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>17.40577</v>
-      </c>
-      <c r="D58" t="n">
-        <v>17.29228</v>
-      </c>
-      <c r="E58" t="n">
-        <v>17.10078</v>
-      </c>
-      <c r="F58" t="n">
-        <v>43.37664</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>17.53799</v>
-      </c>
-      <c r="D59" t="n">
-        <v>17.06974</v>
-      </c>
-      <c r="E59" t="n">
-        <v>17.0784</v>
-      </c>
-      <c r="F59" t="n">
-        <v>43.51199</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>17.2518</v>
-      </c>
-      <c r="D60" t="n">
-        <v>17.43811</v>
-      </c>
-      <c r="E60" t="n">
-        <v>16.83938</v>
-      </c>
-      <c r="F60" t="n">
-        <v>43.00253</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0.77023</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.08304</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.63581</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.97834</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.11003</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.00779</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.09636</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.12995</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0.76234</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.08272</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.63402</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.98358</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.11373</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.00804</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.09633</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.13207</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0.75548</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.08436</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.6276</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.98881</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.11061</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.09464</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.13046</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0.7763600000000001</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.08262</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.6128</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1.00218</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.11212</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.09649000000000001</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.13275</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.76808</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0.0861</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.62449</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1.00236</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0.11219</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.008019999999999999</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.09775</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.13214</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0.76837</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.08588999999999999</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.61002</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.97822</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.11333</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.00778</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.09568</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0.12984</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0.76701</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.08406</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.62613</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.99878</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.11323</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.09553</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.13267</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0.76502</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.08253000000000001</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.62746</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.98545</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.11409</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.09589</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.13075</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0.78811</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.08411</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.62703</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.99456</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0.11237</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.00788</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.09777</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.13029</v>
+        <v>0.1132</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09549000000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12762</v>
       </c>
     </row>
   </sheetData>
